--- a/public/docs_ban_mong/HOBANMONG_BANG_THONG_KE_NEO_6_BE.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_BANG_THONG_KE_NEO_6_BE.xlsx
@@ -2648,7 +2648,7 @@
         <v>6.5</v>
       </c>
       <c r="K40">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L40">
         <v>96.1</v>
@@ -2710,7 +2710,7 @@
         <v>6.5</v>
       </c>
       <c r="K41">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L41">
         <v>96.1</v>
@@ -2772,7 +2772,7 @@
         <v>6.5</v>
       </c>
       <c r="K42">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L42">
         <v>96.1</v>
@@ -2834,7 +2834,7 @@
         <v>6.5</v>
       </c>
       <c r="K43">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L43">
         <v>96.1</v>
@@ -2896,7 +2896,7 @@
         <v>6.5</v>
       </c>
       <c r="K44">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L44">
         <v>96.1</v>
@@ -2958,7 +2958,7 @@
         <v>6.5</v>
       </c>
       <c r="K45">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L45">
         <v>96.1</v>
@@ -3020,7 +3020,7 @@
         <v>6.5</v>
       </c>
       <c r="K46">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L46">
         <v>96.1</v>
@@ -3082,7 +3082,7 @@
         <v>6.5</v>
       </c>
       <c r="K47">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L47">
         <v>96.1</v>
@@ -3144,7 +3144,7 @@
         <v>6.5</v>
       </c>
       <c r="K48">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L48">
         <v>96.1</v>
@@ -3206,7 +3206,7 @@
         <v>6.5</v>
       </c>
       <c r="K49">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L49">
         <v>96.1</v>
@@ -3268,7 +3268,7 @@
         <v>6.5</v>
       </c>
       <c r="K50">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L50">
         <v>96.1</v>
@@ -3330,7 +3330,7 @@
         <v>6.5</v>
       </c>
       <c r="K51">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L51">
         <v>96.1</v>
@@ -3392,7 +3392,7 @@
         <v>6.5</v>
       </c>
       <c r="K52">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L52">
         <v>96.1</v>
@@ -3454,7 +3454,7 @@
         <v>6.5</v>
       </c>
       <c r="K53">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L53">
         <v>96.1</v>
@@ -3516,7 +3516,7 @@
         <v>6.5</v>
       </c>
       <c r="K54">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L54">
         <v>96.1</v>
@@ -3578,7 +3578,7 @@
         <v>6.5</v>
       </c>
       <c r="K55">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L55">
         <v>96.1</v>
@@ -3640,7 +3640,7 @@
         <v>6.5</v>
       </c>
       <c r="K56">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L56">
         <v>96.1</v>
@@ -3702,7 +3702,7 @@
         <v>6.5</v>
       </c>
       <c r="K57">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L57">
         <v>96.1</v>
@@ -3764,7 +3764,7 @@
         <v>6.5</v>
       </c>
       <c r="K58">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L58">
         <v>96.1</v>
@@ -3826,7 +3826,7 @@
         <v>6.5</v>
       </c>
       <c r="K59">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L59">
         <v>96.1</v>
@@ -3888,7 +3888,7 @@
         <v>6.5</v>
       </c>
       <c r="K60">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L60">
         <v>96.1</v>
@@ -3950,7 +3950,7 @@
         <v>6.5</v>
       </c>
       <c r="K61">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L61">
         <v>96.1</v>
@@ -4012,7 +4012,7 @@
         <v>6.5</v>
       </c>
       <c r="K62">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L62">
         <v>96.1</v>
@@ -4074,7 +4074,7 @@
         <v>6.5</v>
       </c>
       <c r="K63">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L63">
         <v>96.1</v>
@@ -4136,7 +4136,7 @@
         <v>6.5</v>
       </c>
       <c r="K64">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L64">
         <v>96.1</v>
@@ -4198,7 +4198,7 @@
         <v>6.5</v>
       </c>
       <c r="K65">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L65">
         <v>96.1</v>
@@ -4260,7 +4260,7 @@
         <v>6.5</v>
       </c>
       <c r="K66">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L66">
         <v>96.1</v>
@@ -4322,7 +4322,7 @@
         <v>6.5</v>
       </c>
       <c r="K67">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L67">
         <v>96.1</v>
@@ -4384,7 +4384,7 @@
         <v>6.5</v>
       </c>
       <c r="K68">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L68">
         <v>96.1</v>
@@ -4446,7 +4446,7 @@
         <v>6.5</v>
       </c>
       <c r="K69">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L69">
         <v>96.1</v>
@@ -4508,7 +4508,7 @@
         <v>6.5</v>
       </c>
       <c r="K70">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L70">
         <v>96.1</v>
@@ -4570,7 +4570,7 @@
         <v>6.5</v>
       </c>
       <c r="K71">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L71">
         <v>96.1</v>
@@ -4632,7 +4632,7 @@
         <v>6.5</v>
       </c>
       <c r="K72">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L72">
         <v>96.1</v>
@@ -4694,7 +4694,7 @@
         <v>6.5</v>
       </c>
       <c r="K73">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L73">
         <v>96.1</v>
@@ -4756,7 +4756,7 @@
         <v>6.5</v>
       </c>
       <c r="K74">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L74">
         <v>96.1</v>
@@ -4818,7 +4818,7 @@
         <v>6.5</v>
       </c>
       <c r="K75">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L75">
         <v>96.1</v>
@@ -4880,7 +4880,7 @@
         <v>6.5</v>
       </c>
       <c r="K76">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L76">
         <v>96.1</v>
@@ -4942,7 +4942,7 @@
         <v>6.5</v>
       </c>
       <c r="K77">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L77">
         <v>96.1</v>
@@ -5004,7 +5004,7 @@
         <v>6.5</v>
       </c>
       <c r="K78">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L78">
         <v>96.1</v>
@@ -5066,7 +5066,7 @@
         <v>6.5</v>
       </c>
       <c r="K79">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L79">
         <v>96.1</v>
@@ -5128,7 +5128,7 @@
         <v>6.5</v>
       </c>
       <c r="K80">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="L80">
         <v>96.1</v>
@@ -5190,7 +5190,7 @@
         <v>6.5</v>
       </c>
       <c r="K81">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L81">
         <v>81.9</v>
@@ -5252,7 +5252,7 @@
         <v>6.5</v>
       </c>
       <c r="K82">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L82">
         <v>81.9</v>
@@ -5314,7 +5314,7 @@
         <v>6.5</v>
       </c>
       <c r="K83">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L83">
         <v>81.9</v>
@@ -5376,7 +5376,7 @@
         <v>6.5</v>
       </c>
       <c r="K84">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L84">
         <v>81.9</v>
@@ -5438,7 +5438,7 @@
         <v>6.5</v>
       </c>
       <c r="K85">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L85">
         <v>81.9</v>
@@ -5500,7 +5500,7 @@
         <v>6.5</v>
       </c>
       <c r="K86">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L86">
         <v>81.9</v>
@@ -5562,7 +5562,7 @@
         <v>6.5</v>
       </c>
       <c r="K87">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L87">
         <v>81.9</v>
@@ -5624,7 +5624,7 @@
         <v>6.5</v>
       </c>
       <c r="K88">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L88">
         <v>81.9</v>
@@ -5686,7 +5686,7 @@
         <v>6.5</v>
       </c>
       <c r="K89">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L89">
         <v>81.9</v>
@@ -5748,7 +5748,7 @@
         <v>6.5</v>
       </c>
       <c r="K90">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L90">
         <v>81.9</v>
@@ -5810,7 +5810,7 @@
         <v>6.5</v>
       </c>
       <c r="K91">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L91">
         <v>81.9</v>
@@ -5872,7 +5872,7 @@
         <v>6.5</v>
       </c>
       <c r="K92">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L92">
         <v>81.9</v>
@@ -5934,7 +5934,7 @@
         <v>6.5</v>
       </c>
       <c r="K93">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L93">
         <v>81.9</v>
@@ -5996,7 +5996,7 @@
         <v>6.5</v>
       </c>
       <c r="K94">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L94">
         <v>81.9</v>
@@ -6058,7 +6058,7 @@
         <v>6.5</v>
       </c>
       <c r="K95">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="L95">
         <v>81.9</v>
@@ -6120,7 +6120,7 @@
         <v>6.5</v>
       </c>
       <c r="K96">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L96">
         <v>96.1</v>
@@ -6182,7 +6182,7 @@
         <v>6.5</v>
       </c>
       <c r="K97">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L97">
         <v>96.1</v>
@@ -6244,7 +6244,7 @@
         <v>6.5</v>
       </c>
       <c r="K98">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L98">
         <v>96.1</v>
@@ -6306,7 +6306,7 @@
         <v>6.5</v>
       </c>
       <c r="K99">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L99">
         <v>96.1</v>
@@ -6368,7 +6368,7 @@
         <v>6.5</v>
       </c>
       <c r="K100">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L100">
         <v>96.1</v>
@@ -6430,7 +6430,7 @@
         <v>6.5</v>
       </c>
       <c r="K101">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L101">
         <v>96.1</v>
@@ -6492,7 +6492,7 @@
         <v>6.5</v>
       </c>
       <c r="K102">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L102">
         <v>96.1</v>
@@ -6554,7 +6554,7 @@
         <v>6.5</v>
       </c>
       <c r="K103">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L103">
         <v>96.1</v>
@@ -6616,7 +6616,7 @@
         <v>6.5</v>
       </c>
       <c r="K104">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L104">
         <v>96.1</v>
@@ -6678,7 +6678,7 @@
         <v>6.5</v>
       </c>
       <c r="K105">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L105">
         <v>96.1</v>
@@ -6740,7 +6740,7 @@
         <v>6.5</v>
       </c>
       <c r="K106">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L106">
         <v>96.1</v>
@@ -6802,7 +6802,7 @@
         <v>6.5</v>
       </c>
       <c r="K107">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L107">
         <v>96.1</v>
@@ -6864,7 +6864,7 @@
         <v>6.5</v>
       </c>
       <c r="K108">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L108">
         <v>96.1</v>
@@ -6926,7 +6926,7 @@
         <v>6.5</v>
       </c>
       <c r="K109">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L109">
         <v>96.1</v>
@@ -6988,7 +6988,7 @@
         <v>6.5</v>
       </c>
       <c r="K110">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L110">
         <v>96.1</v>
@@ -7050,7 +7050,7 @@
         <v>6.5</v>
       </c>
       <c r="K111">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L111">
         <v>96.1</v>
@@ -7112,7 +7112,7 @@
         <v>6.5</v>
       </c>
       <c r="K112">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L112">
         <v>96.1</v>
@@ -7174,7 +7174,7 @@
         <v>6.5</v>
       </c>
       <c r="K113">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L113">
         <v>96.1</v>
@@ -7236,7 +7236,7 @@
         <v>6.5</v>
       </c>
       <c r="K114">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L114">
         <v>96.1</v>
@@ -7298,7 +7298,7 @@
         <v>6.5</v>
       </c>
       <c r="K115">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L115">
         <v>96.1</v>
@@ -7360,7 +7360,7 @@
         <v>6.5</v>
       </c>
       <c r="K116">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L116">
         <v>96.1</v>
@@ -7422,7 +7422,7 @@
         <v>6.5</v>
       </c>
       <c r="K117">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="L117">
         <v>96.1</v>
@@ -7484,7 +7484,7 @@
         <v>6.5</v>
       </c>
       <c r="K118">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L118">
         <v>81.9</v>
@@ -7546,7 +7546,7 @@
         <v>6.5</v>
       </c>
       <c r="K119">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L119">
         <v>81.9</v>
@@ -7608,7 +7608,7 @@
         <v>6.5</v>
       </c>
       <c r="K120">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L120">
         <v>81.9</v>
@@ -7670,7 +7670,7 @@
         <v>6.5</v>
       </c>
       <c r="K121">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L121">
         <v>81.9</v>
@@ -7732,7 +7732,7 @@
         <v>6.5</v>
       </c>
       <c r="K122">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L122">
         <v>81.9</v>
@@ -7794,7 +7794,7 @@
         <v>6.5</v>
       </c>
       <c r="K123">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L123">
         <v>81.9</v>
@@ -7856,7 +7856,7 @@
         <v>6.5</v>
       </c>
       <c r="K124">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L124">
         <v>81.9</v>
@@ -7918,7 +7918,7 @@
         <v>6.5</v>
       </c>
       <c r="K125">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L125">
         <v>81.9</v>
@@ -7980,7 +7980,7 @@
         <v>6.5</v>
       </c>
       <c r="K126">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L126">
         <v>81.9</v>
@@ -8042,7 +8042,7 @@
         <v>6.5</v>
       </c>
       <c r="K127">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L127">
         <v>81.9</v>
@@ -8104,7 +8104,7 @@
         <v>6.5</v>
       </c>
       <c r="K128">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L128">
         <v>81.9</v>
@@ -8166,7 +8166,7 @@
         <v>6.5</v>
       </c>
       <c r="K129">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L129">
         <v>81.9</v>
@@ -8228,7 +8228,7 @@
         <v>6.5</v>
       </c>
       <c r="K130">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L130">
         <v>81.9</v>
@@ -8290,7 +8290,7 @@
         <v>6.5</v>
       </c>
       <c r="K131">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L131">
         <v>81.9</v>
@@ -8352,7 +8352,7 @@
         <v>6.5</v>
       </c>
       <c r="K132">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L132">
         <v>81.9</v>
@@ -8414,7 +8414,7 @@
         <v>6.5</v>
       </c>
       <c r="K133">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L133">
         <v>81.9</v>
@@ -8476,7 +8476,7 @@
         <v>6.5</v>
       </c>
       <c r="K134">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L134">
         <v>81.9</v>
@@ -8538,7 +8538,7 @@
         <v>6.5</v>
       </c>
       <c r="K135">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L135">
         <v>81.9</v>
@@ -8600,7 +8600,7 @@
         <v>6.5</v>
       </c>
       <c r="K136">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L136">
         <v>81.9</v>
@@ -8662,7 +8662,7 @@
         <v>6.5</v>
       </c>
       <c r="K137">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L137">
         <v>81.9</v>
@@ -8724,7 +8724,7 @@
         <v>6.5</v>
       </c>
       <c r="K138">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L138">
         <v>81.9</v>
@@ -8786,7 +8786,7 @@
         <v>6.5</v>
       </c>
       <c r="K139">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L139">
         <v>81.9</v>
@@ -8848,7 +8848,7 @@
         <v>6.5</v>
       </c>
       <c r="K140">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L140">
         <v>81.9</v>
@@ -8910,7 +8910,7 @@
         <v>6.5</v>
       </c>
       <c r="K141">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L141">
         <v>81.9</v>
@@ -8972,7 +8972,7 @@
         <v>6.5</v>
       </c>
       <c r="K142">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L142">
         <v>81.9</v>
@@ -9034,7 +9034,7 @@
         <v>6.5</v>
       </c>
       <c r="K143">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L143">
         <v>81.9</v>
@@ -9096,7 +9096,7 @@
         <v>6.5</v>
       </c>
       <c r="K144">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="L144">
         <v>81.9</v>
@@ -9158,7 +9158,7 @@
         <v>6.5</v>
       </c>
       <c r="K145">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L145">
         <v>81.9</v>
@@ -9220,7 +9220,7 @@
         <v>6.5</v>
       </c>
       <c r="K146">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L146">
         <v>81.9</v>
@@ -9282,7 +9282,7 @@
         <v>6.5</v>
       </c>
       <c r="K147">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L147">
         <v>81.9</v>
@@ -9344,7 +9344,7 @@
         <v>6.5</v>
       </c>
       <c r="K148">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L148">
         <v>81.9</v>
@@ -9406,7 +9406,7 @@
         <v>6.5</v>
       </c>
       <c r="K149">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L149">
         <v>81.9</v>
@@ -9468,7 +9468,7 @@
         <v>6.5</v>
       </c>
       <c r="K150">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L150">
         <v>81.9</v>
@@ -9530,7 +9530,7 @@
         <v>6.5</v>
       </c>
       <c r="K151">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L151">
         <v>81.9</v>
@@ -9592,7 +9592,7 @@
         <v>6.5</v>
       </c>
       <c r="K152">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L152">
         <v>81.9</v>
@@ -9654,7 +9654,7 @@
         <v>6.5</v>
       </c>
       <c r="K153">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L153">
         <v>81.9</v>
@@ -9716,7 +9716,7 @@
         <v>6.5</v>
       </c>
       <c r="K154">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L154">
         <v>81.9</v>
@@ -9778,7 +9778,7 @@
         <v>6.5</v>
       </c>
       <c r="K155">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L155">
         <v>81.9</v>
@@ -9840,7 +9840,7 @@
         <v>6.5</v>
       </c>
       <c r="K156">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L156">
         <v>81.9</v>
@@ -9902,7 +9902,7 @@
         <v>6.5</v>
       </c>
       <c r="K157">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L157">
         <v>81.9</v>
@@ -9964,7 +9964,7 @@
         <v>6.5</v>
       </c>
       <c r="K158">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L158">
         <v>81.9</v>
@@ -10026,7 +10026,7 @@
         <v>6.5</v>
       </c>
       <c r="K159">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L159">
         <v>81.9</v>
@@ -10088,7 +10088,7 @@
         <v>6.5</v>
       </c>
       <c r="K160">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L160">
         <v>81.9</v>
@@ -10150,7 +10150,7 @@
         <v>6.5</v>
       </c>
       <c r="K161">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L161">
         <v>81.9</v>
@@ -10212,7 +10212,7 @@
         <v>6.5</v>
       </c>
       <c r="K162">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L162">
         <v>81.9</v>
@@ -10274,7 +10274,7 @@
         <v>6.5</v>
       </c>
       <c r="K163">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L163">
         <v>81.9</v>
@@ -10336,7 +10336,7 @@
         <v>6.5</v>
       </c>
       <c r="K164">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L164">
         <v>81.9</v>
@@ -10398,7 +10398,7 @@
         <v>6.5</v>
       </c>
       <c r="K165">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L165">
         <v>81.9</v>
@@ -10460,7 +10460,7 @@
         <v>6.5</v>
       </c>
       <c r="K166">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L166">
         <v>81.9</v>
@@ -10522,7 +10522,7 @@
         <v>6.5</v>
       </c>
       <c r="K167">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L167">
         <v>81.9</v>
@@ -10584,7 +10584,7 @@
         <v>6.5</v>
       </c>
       <c r="K168">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L168">
         <v>81.9</v>
@@ -10646,7 +10646,7 @@
         <v>6.5</v>
       </c>
       <c r="K169">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L169">
         <v>81.9</v>
@@ -10708,7 +10708,7 @@
         <v>6.5</v>
       </c>
       <c r="K170">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L170">
         <v>81.9</v>
@@ -10770,7 +10770,7 @@
         <v>6.5</v>
       </c>
       <c r="K171">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L171">
         <v>81.9</v>
@@ -10832,7 +10832,7 @@
         <v>6.5</v>
       </c>
       <c r="K172">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L172">
         <v>81.9</v>
@@ -10894,7 +10894,7 @@
         <v>6.5</v>
       </c>
       <c r="K173">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L173">
         <v>81.9</v>
@@ -10956,7 +10956,7 @@
         <v>6.5</v>
       </c>
       <c r="K174">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L174">
         <v>81.9</v>
@@ -11018,7 +11018,7 @@
         <v>6.5</v>
       </c>
       <c r="K175">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L175">
         <v>81.9</v>
@@ -11080,7 +11080,7 @@
         <v>6.5</v>
       </c>
       <c r="K176">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L176">
         <v>81.9</v>
@@ -11142,7 +11142,7 @@
         <v>6.5</v>
       </c>
       <c r="K177">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L177">
         <v>81.9</v>
@@ -11204,7 +11204,7 @@
         <v>6.5</v>
       </c>
       <c r="K178">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L178">
         <v>81.9</v>
@@ -11266,7 +11266,7 @@
         <v>6.5</v>
       </c>
       <c r="K179">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L179">
         <v>81.9</v>
@@ -11328,7 +11328,7 @@
         <v>6.5</v>
       </c>
       <c r="K180">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L180">
         <v>81.9</v>
@@ -11390,7 +11390,7 @@
         <v>6.5</v>
       </c>
       <c r="K181">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L181">
         <v>81.9</v>
@@ -11452,7 +11452,7 @@
         <v>6.5</v>
       </c>
       <c r="K182">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L182">
         <v>81.9</v>
@@ -11514,7 +11514,7 @@
         <v>6.5</v>
       </c>
       <c r="K183">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L183">
         <v>81.9</v>
@@ -11576,7 +11576,7 @@
         <v>6.5</v>
       </c>
       <c r="K184">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L184">
         <v>81.9</v>
@@ -11638,7 +11638,7 @@
         <v>6.5</v>
       </c>
       <c r="K185">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L185">
         <v>81.9</v>
@@ -11700,7 +11700,7 @@
         <v>6.5</v>
       </c>
       <c r="K186">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L186">
         <v>81.9</v>
@@ -11762,7 +11762,7 @@
         <v>6.5</v>
       </c>
       <c r="K187">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L187">
         <v>81.9</v>
@@ -11824,7 +11824,7 @@
         <v>6.5</v>
       </c>
       <c r="K188">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L188">
         <v>81.9</v>
@@ -11886,7 +11886,7 @@
         <v>6.5</v>
       </c>
       <c r="K189">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="L189">
         <v>81.9</v>
@@ -12097,7 +12097,7 @@
         <v>15.2</v>
       </c>
       <c r="Q6">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="R6">
         <v>0.86</v>
@@ -12171,7 +12171,7 @@
         <v>14.8</v>
       </c>
       <c r="Q7">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="R7">
         <v>0.95</v>
@@ -12245,7 +12245,7 @@
         <v>14.8</v>
       </c>
       <c r="Q8">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="R8">
         <v>0.94</v>
@@ -12319,13 +12319,13 @@
         <v>15.2</v>
       </c>
       <c r="Q9">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="R9">
         <v>0.9</v>
       </c>
       <c r="S9">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="T9">
         <v>0.98</v>
@@ -12467,7 +12467,7 @@
         <v>14.8</v>
       </c>
       <c r="Q11">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="R11">
         <v>0.95</v>
@@ -12541,19 +12541,19 @@
         <v>14.8</v>
       </c>
       <c r="Q12">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="R12">
         <v>0.91</v>
       </c>
       <c r="S12">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="T12">
         <v>0.97</v>
       </c>
       <c r="U12">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="V12">
         <v>0.15</v>
@@ -12615,13 +12615,13 @@
         <v>14.8</v>
       </c>
       <c r="Q13">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="R13">
         <v>0.96</v>
       </c>
       <c r="S13">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="T13">
         <v>0.99</v>
@@ -12689,7 +12689,7 @@
         <v>14.8</v>
       </c>
       <c r="Q14">
-        <v>85.5</v>
+        <v>85.4</v>
       </c>
       <c r="R14">
         <v>0.69</v>
@@ -12763,7 +12763,7 @@
         <v>15.2</v>
       </c>
       <c r="Q15">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R15">
         <v>0.81</v>
@@ -12775,7 +12775,7 @@
         <v>0.99</v>
       </c>
       <c r="U15">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="V15">
         <v>0.18</v>
@@ -12837,13 +12837,13 @@
         <v>14.8</v>
       </c>
       <c r="Q16">
-        <v>71.1</v>
+        <v>71.2</v>
       </c>
       <c r="R16">
         <v>0.74</v>
       </c>
       <c r="S16">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="T16">
         <v>0.93</v>
@@ -12985,7 +12985,7 @@
         <v>15.6</v>
       </c>
       <c r="Q18">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="R18">
         <v>0.83</v>
@@ -12994,10 +12994,10 @@
         <v>0.44</v>
       </c>
       <c r="T18">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="U18">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="V18">
         <v>0.22</v>
@@ -13059,19 +13059,19 @@
         <v>15.2</v>
       </c>
       <c r="Q19">
-        <v>78.4</v>
+        <v>78.6</v>
       </c>
       <c r="R19">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="S19">
         <v>0.44</v>
       </c>
       <c r="T19">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="U19">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="V19">
         <v>0.18</v>
@@ -13207,7 +13207,7 @@
         <v>14.8</v>
       </c>
       <c r="Q21">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="R21">
         <v>0.79</v>
@@ -13219,7 +13219,7 @@
         <v>0.96</v>
       </c>
       <c r="U21">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="V21">
         <v>0.15</v>
@@ -13281,7 +13281,7 @@
         <v>14.8</v>
       </c>
       <c r="Q22">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="R22">
         <v>0.74</v>
@@ -13355,19 +13355,19 @@
         <v>15.2</v>
       </c>
       <c r="Q23">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R23">
         <v>0.84</v>
       </c>
       <c r="S23">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="T23">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="U23">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="V23">
         <v>0.18</v>
@@ -13429,7 +13429,7 @@
         <v>15.6</v>
       </c>
       <c r="Q24">
-        <v>79.2</v>
+        <v>79.4</v>
       </c>
       <c r="R24">
         <v>0.83</v>
@@ -13441,7 +13441,7 @@
         <v>0.98</v>
       </c>
       <c r="U24">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="V24">
         <v>0.22</v>
@@ -13503,10 +13503,10 @@
         <v>14.8</v>
       </c>
       <c r="Q25">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="R25">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="S25">
         <v>0.33</v>
@@ -13577,19 +13577,19 @@
         <v>14.8</v>
       </c>
       <c r="Q26">
-        <v>54.6</v>
+        <v>53.8</v>
       </c>
       <c r="R26">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="S26">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="T26">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="U26">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="V26">
         <v>0.15</v>
@@ -13651,7 +13651,7 @@
         <v>14.8</v>
       </c>
       <c r="Q27">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="R27">
         <v>0.72</v>
@@ -13704,43 +13704,43 @@
         <v>239.6</v>
       </c>
       <c r="J28">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K28">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L28">
-        <v>5.26</v>
+        <v>5.37</v>
       </c>
       <c r="M28">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="N28">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="O28">
         <v>4</v>
       </c>
       <c r="P28">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="Q28">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
       <c r="R28">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="S28">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="T28">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="U28">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="V28">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="W28" t="str">
         <v>ĐẠT</v>
@@ -13811,7 +13811,7 @@
         <v>0.91</v>
       </c>
       <c r="U29">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="V29">
         <v>0.15</v>
@@ -13873,13 +13873,13 @@
         <v>14.8</v>
       </c>
       <c r="Q30">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="R30">
         <v>0.82</v>
       </c>
       <c r="S30">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="T30">
         <v>0.8</v>
@@ -13947,7 +13947,7 @@
         <v>14.8</v>
       </c>
       <c r="Q31">
-        <v>57.5</v>
+        <v>57.3</v>
       </c>
       <c r="R31">
         <v>0.84</v>
@@ -13959,7 +13959,7 @@
         <v>0.95</v>
       </c>
       <c r="U31">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="V31">
         <v>0.15</v>
@@ -14021,7 +14021,7 @@
         <v>14.8</v>
       </c>
       <c r="Q32">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="R32">
         <v>0.88</v>
@@ -14033,7 +14033,7 @@
         <v>0.87</v>
       </c>
       <c r="U32">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="V32">
         <v>0.15</v>
@@ -14095,13 +14095,13 @@
         <v>14.8</v>
       </c>
       <c r="Q33">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="R33">
         <v>0.9</v>
       </c>
       <c r="S33">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="T33">
         <v>0.96</v>
@@ -14169,13 +14169,13 @@
         <v>14.8</v>
       </c>
       <c r="Q34">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="R34">
         <v>0.89</v>
       </c>
       <c r="S34">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="T34">
         <v>0.89</v>
@@ -14243,7 +14243,7 @@
         <v>14.8</v>
       </c>
       <c r="Q35">
-        <v>58</v>
+        <v>57.9</v>
       </c>
       <c r="R35">
         <v>0.63</v>
@@ -14317,16 +14317,16 @@
         <v>15.2</v>
       </c>
       <c r="Q36">
-        <v>150.4</v>
+        <v>152.1</v>
       </c>
       <c r="R36">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="S36">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="T36">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -14391,19 +14391,19 @@
         <v>14.8</v>
       </c>
       <c r="Q37">
-        <v>109.9</v>
+        <v>110.8</v>
       </c>
       <c r="R37">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="S37">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="T37">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="U37">
-        <v>0.56</v>
+        <v>0.59</v>
       </c>
       <c r="V37">
         <v>0.15</v>
@@ -14444,43 +14444,43 @@
         <v>305</v>
       </c>
       <c r="J38">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="K38">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L38">
-        <v>7.01</v>
+        <v>7.21</v>
       </c>
       <c r="M38">
-        <v>259</v>
+        <v>339</v>
       </c>
       <c r="N38">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="O38">
         <v>4</v>
       </c>
       <c r="P38">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="Q38">
-        <v>113.9</v>
+        <v>114.9</v>
       </c>
       <c r="R38">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="S38">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="T38">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="U38">
-        <v>0.55</v>
+        <v>0.28</v>
       </c>
       <c r="V38">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="W38" t="str">
         <v>ĐẠT</v>
@@ -14539,19 +14539,19 @@
         <v>14.8</v>
       </c>
       <c r="Q39">
-        <v>64.6</v>
+        <v>64.9</v>
       </c>
       <c r="R39">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="S39">
         <v>0.64</v>
       </c>
       <c r="T39">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="U39">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="V39">
         <v>0.15</v>
@@ -14613,7 +14613,7 @@
         <v>14.8</v>
       </c>
       <c r="Q40">
-        <v>109</v>
+        <v>109.7</v>
       </c>
       <c r="R40">
         <v>0.71</v>
@@ -14622,10 +14622,10 @@
         <v>0.67</v>
       </c>
       <c r="T40">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="U40">
-        <v>0.54</v>
+        <v>0.56</v>
       </c>
       <c r="V40">
         <v>0.15</v>
@@ -14685,7 +14685,7 @@
         <v>Tổng bê tông đế</v>
       </c>
       <c r="B46">
-        <v>173.3</v>
+        <v>173.6</v>
       </c>
       <c r="C46" t="str">
         <v>m³</v>
@@ -14696,7 +14696,7 @@
         <v>Tổng thép bản đế (ước tính)</v>
       </c>
       <c r="B47">
-        <v>7.25</v>
+        <v>7.29</v>
       </c>
       <c r="C47" t="str">
         <v>tấn</v>
@@ -14876,7 +14876,7 @@
         <v>55.9</v>
       </c>
       <c r="H4">
-        <v>85.4</v>
+        <v>85.3</v>
       </c>
       <c r="I4">
         <v>71</v>
@@ -14929,10 +14929,10 @@
         <v>69.6</v>
       </c>
       <c r="H5">
-        <v>80.1</v>
+        <v>80.3</v>
       </c>
       <c r="I5">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="J5">
         <v>0.78</v>
@@ -14982,10 +14982,10 @@
         <v>62.9</v>
       </c>
       <c r="H6">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="I6">
-        <v>73.5</v>
+        <v>73.7</v>
       </c>
       <c r="J6">
         <v>0.75</v>
@@ -14997,7 +14997,7 @@
         <v>0.94</v>
       </c>
       <c r="M6">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="N6">
         <v>0.15</v>
@@ -15035,22 +15035,22 @@
         <v>67.7</v>
       </c>
       <c r="H7">
-        <v>76.7</v>
+        <v>75.6</v>
       </c>
       <c r="I7">
-        <v>71.8</v>
+        <v>70.8</v>
       </c>
       <c r="J7">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="K7">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="L7">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="M7">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="N7">
         <v>0.15</v>
@@ -15088,10 +15088,10 @@
         <v>61.1</v>
       </c>
       <c r="H8">
-        <v>105.6</v>
+        <v>105.3</v>
       </c>
       <c r="I8">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="J8">
         <v>0.73</v>
@@ -15103,7 +15103,7 @@
         <v>0.98</v>
       </c>
       <c r="M8">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="N8">
         <v>0.18</v>
@@ -15141,22 +15141,22 @@
         <v>49</v>
       </c>
       <c r="H9">
-        <v>150</v>
+        <v>151.7</v>
       </c>
       <c r="I9">
-        <v>113.4</v>
+        <v>114.7</v>
       </c>
       <c r="J9">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="K9">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="L9">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N9">
         <v>0.15</v>
@@ -15180,7 +15180,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI60"/>
+  <dimension ref="A1:AI61"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -15368,7 +15368,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="F7">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="G7">
         <v>15.3</v>
@@ -15380,7 +15380,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="J7">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="K7">
         <v>15.3</v>
@@ -15407,7 +15407,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S7">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="T7">
         <v>88.1</v>
@@ -15487,7 +15487,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="J8">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="K8">
         <v>15.15</v>
@@ -15514,7 +15514,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S8">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="T8">
         <v>76.4</v>
@@ -15582,7 +15582,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="F9">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="G9">
         <v>15.66</v>
@@ -15594,7 +15594,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="J9">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="K9">
         <v>15.68</v>
@@ -15621,7 +15621,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
         <v>83.5</v>
@@ -15689,7 +15689,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="F10">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="G10">
         <v>16.16</v>
@@ -15701,7 +15701,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="J10">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="K10">
         <v>16.16</v>
@@ -15728,7 +15728,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T10">
         <v>82.8</v>
@@ -15755,7 +15755,7 @@
         <v>0.9</v>
       </c>
       <c r="AB10">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AC10">
         <v>0.98</v>
@@ -15835,10 +15835,10 @@
         <v>B1-D27 căng (MN cao)</v>
       </c>
       <c r="S11">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="T11">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="U11">
         <v>3.5</v>
@@ -15903,7 +15903,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="F12">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="G12">
         <v>15.02</v>
@@ -15915,7 +15915,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="J12">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="K12">
         <v>15.02</v>
@@ -15942,10 +15942,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="T12">
-        <v>76.4</v>
+        <v>76.5</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -16010,7 +16010,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="F13">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="G13">
         <v>15.67</v>
@@ -16022,7 +16022,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="J13">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="K13">
         <v>15.67</v>
@@ -16049,10 +16049,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S13">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T13">
-        <v>80.8</v>
+        <v>80.9</v>
       </c>
       <c r="U13">
         <v>3.25</v>
@@ -16076,13 +16076,13 @@
         <v>0.91</v>
       </c>
       <c r="AB13">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AC13">
         <v>0.97</v>
       </c>
       <c r="AD13">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AE13">
         <v>0.15</v>
@@ -16129,7 +16129,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="J14">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="K14">
         <v>15.01</v>
@@ -16156,10 +16156,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S14">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="T14">
-        <v>76.8</v>
+        <v>76.9</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -16183,7 +16183,7 @@
         <v>0.96</v>
       </c>
       <c r="AB14">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AC14">
         <v>0.99</v>
@@ -16224,7 +16224,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="F15">
-        <v>85.5</v>
+        <v>85.4</v>
       </c>
       <c r="G15">
         <v>17.51</v>
@@ -16266,7 +16266,7 @@
         <v>52.8</v>
       </c>
       <c r="T15">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="U15">
         <v>3.5</v>
@@ -16331,7 +16331,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="F16">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="G16">
         <v>15.96</v>
@@ -16343,7 +16343,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="J16">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="K16">
         <v>15.25</v>
@@ -16370,10 +16370,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S16">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="T16">
-        <v>102.4</v>
+        <v>102.6</v>
       </c>
       <c r="U16">
         <v>3.75</v>
@@ -16403,7 +16403,7 @@
         <v>0.99</v>
       </c>
       <c r="AD16">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="AE16">
         <v>0.18</v>
@@ -16438,7 +16438,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="F17">
-        <v>71.1</v>
+        <v>71.2</v>
       </c>
       <c r="G17">
         <v>8.41</v>
@@ -16450,7 +16450,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="J17">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="K17">
         <v>16.43</v>
@@ -16480,7 +16480,7 @@
         <v>42.8</v>
       </c>
       <c r="T17">
-        <v>113.1</v>
+        <v>113.3</v>
       </c>
       <c r="U17">
         <v>4.75</v>
@@ -16504,7 +16504,7 @@
         <v>0.74</v>
       </c>
       <c r="AB17">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="AC17">
         <v>0.93</v>
@@ -16584,7 +16584,7 @@
         <v>B2-D23 căng (MN cao)</v>
       </c>
       <c r="S18">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="T18">
         <v>24</v>
@@ -16652,7 +16652,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="F19">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="G19">
         <v>8.34</v>
@@ -16664,7 +16664,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="J19">
-        <v>68.4</v>
+        <v>67.5</v>
       </c>
       <c r="K19">
         <v>8.35</v>
@@ -16691,10 +16691,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S19">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T19">
-        <v>133.8</v>
+        <v>133.1</v>
       </c>
       <c r="U19">
         <v>4</v>
@@ -16721,10 +16721,10 @@
         <v>0.44</v>
       </c>
       <c r="AC19">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AD19">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="AE19">
         <v>0.22</v>
@@ -16733,7 +16733,7 @@
         <v>0.97</v>
       </c>
       <c r="AG19">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AH19" t="str">
         <v>ĐẠT</v>
@@ -16759,7 +16759,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="F20">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="G20">
         <v>12.9</v>
@@ -16771,7 +16771,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="J20">
-        <v>78.4</v>
+        <v>78.6</v>
       </c>
       <c r="K20">
         <v>12.9</v>
@@ -16798,10 +16798,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S20">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="T20">
-        <v>116.6</v>
+        <v>116.8</v>
       </c>
       <c r="U20">
         <v>4</v>
@@ -16822,16 +16822,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA20">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AB20">
         <v>0.44</v>
       </c>
       <c r="AC20">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AD20">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="AE20">
         <v>0.18</v>
@@ -16840,7 +16840,7 @@
         <v>0.8</v>
       </c>
       <c r="AG20">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AH20" t="str">
         <v>ĐẠT</v>
@@ -16905,7 +16905,7 @@
         <v>B2-D34 căng (MN cao)</v>
       </c>
       <c r="S21">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="T21">
         <v>24</v>
@@ -16985,7 +16985,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="J22">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="K22">
         <v>14.29</v>
@@ -17012,10 +17012,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S22">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T22">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="U22">
         <v>3.5</v>
@@ -17045,7 +17045,7 @@
         <v>0.96</v>
       </c>
       <c r="AD22">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AE22">
         <v>0.15</v>
@@ -17080,7 +17080,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="F23">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="G23">
         <v>23.35</v>
@@ -17092,7 +17092,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="J23">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="K23">
         <v>14.25</v>
@@ -17119,10 +17119,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S23">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="T23">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="U23">
         <v>3</v>
@@ -17187,7 +17187,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="F24">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="G24">
         <v>9.52</v>
@@ -17199,7 +17199,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="J24">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="K24">
         <v>9.52</v>
@@ -17226,10 +17226,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S24">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="T24">
-        <v>117.6</v>
+        <v>116.7</v>
       </c>
       <c r="U24">
         <v>4</v>
@@ -17253,13 +17253,13 @@
         <v>0.84</v>
       </c>
       <c r="AB24">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AC24">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="AD24">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="AE24">
         <v>0.18</v>
@@ -17268,7 +17268,7 @@
         <v>0.8</v>
       </c>
       <c r="AG24">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="AH24" t="str">
         <v>ĐẠT</v>
@@ -17294,7 +17294,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="F25">
-        <v>79.2</v>
+        <v>79.4</v>
       </c>
       <c r="G25">
         <v>11.47</v>
@@ -17306,7 +17306,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="J25">
-        <v>72.1</v>
+        <v>72.2</v>
       </c>
       <c r="K25">
         <v>11.47</v>
@@ -17336,7 +17336,7 @@
         <v>3.3</v>
       </c>
       <c r="T25">
-        <v>134.1</v>
+        <v>134.4</v>
       </c>
       <c r="U25">
         <v>4</v>
@@ -17366,7 +17366,7 @@
         <v>0.98</v>
       </c>
       <c r="AD25">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="AE25">
         <v>0.22</v>
@@ -17401,7 +17401,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="F26">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="G26">
         <v>17.5</v>
@@ -17440,10 +17440,10 @@
         <v>B3-D16 căng (MN cao)</v>
       </c>
       <c r="S26">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="T26">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="U26">
         <v>2.5</v>
@@ -17464,7 +17464,7 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA26">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AB26">
         <v>0.33</v>
@@ -17508,7 +17508,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="F27">
-        <v>54.6</v>
+        <v>53.8</v>
       </c>
       <c r="G27">
         <v>17.5</v>
@@ -17547,10 +17547,10 @@
         <v>B3-D18 căng (MN cao)</v>
       </c>
       <c r="S27">
-        <v>38.8</v>
+        <v>38.3</v>
       </c>
       <c r="T27">
-        <v>38.4</v>
+        <v>37.8</v>
       </c>
       <c r="U27">
         <v>2.5</v>
@@ -17571,16 +17571,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA27">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="AB27">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="AC27">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="AD27">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AE27">
         <v>0.15</v>
@@ -17589,7 +17589,7 @@
         <v>0.62</v>
       </c>
       <c r="AG27">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="AH27" t="str">
         <v>ĐẠT</v>
@@ -17615,7 +17615,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="F28">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="G28">
         <v>28.75</v>
@@ -17627,7 +17627,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="J28">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="K28">
         <v>28.76</v>
@@ -17654,7 +17654,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S28">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="T28">
         <v>47.1</v>
@@ -17722,7 +17722,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="F29">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
       <c r="G29">
         <v>15.56</v>
@@ -17734,7 +17734,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="J29">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="K29">
         <v>15.57</v>
@@ -17761,49 +17761,49 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S29">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T29">
-        <v>93.3</v>
+        <v>93.1</v>
       </c>
       <c r="U29">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W29">
-        <v>79.2</v>
+        <v>81</v>
       </c>
       <c r="X29">
-        <v>5.26</v>
+        <v>5.37</v>
       </c>
       <c r="Y29">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="Z29" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="AA29">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="AB29">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AC29">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AD29">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="AE29">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="AF29">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AG29">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AH29" t="str">
         <v>ĐẠT</v>
@@ -17841,7 +17841,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="J30">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="K30">
         <v>22.12</v>
@@ -17868,10 +17868,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S30">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="T30">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="U30">
         <v>2.5</v>
@@ -17901,7 +17901,7 @@
         <v>0.91</v>
       </c>
       <c r="AD30">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AE30">
         <v>0.15</v>
@@ -17936,7 +17936,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="F31">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="G31">
         <v>25.35</v>
@@ -17948,7 +17948,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="J31">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="K31">
         <v>25.37</v>
@@ -17975,7 +17975,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T31">
         <v>53.5</v>
@@ -18002,7 +18002,7 @@
         <v>0.82</v>
       </c>
       <c r="AB31">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="AC31">
         <v>0.8</v>
@@ -18043,7 +18043,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="F32">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="G32">
         <v>13</v>
@@ -18055,7 +18055,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="J32">
-        <v>57.5</v>
+        <v>57.3</v>
       </c>
       <c r="K32">
         <v>13.07</v>
@@ -18082,10 +18082,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S32">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="T32">
-        <v>74.9</v>
+        <v>74.8</v>
       </c>
       <c r="U32">
         <v>3.25</v>
@@ -18115,7 +18115,7 @@
         <v>0.95</v>
       </c>
       <c r="AD32">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AE32">
         <v>0.15</v>
@@ -18150,7 +18150,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="F33">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="G33">
         <v>19.34</v>
@@ -18162,7 +18162,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="J33">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="K33">
         <v>19.34</v>
@@ -18189,7 +18189,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S33">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T33">
         <v>57.4</v>
@@ -18222,7 +18222,7 @@
         <v>0.87</v>
       </c>
       <c r="AD33">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AE33">
         <v>0.15</v>
@@ -18257,7 +18257,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="F34">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="G34">
         <v>11.33</v>
@@ -18269,7 +18269,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="J34">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="K34">
         <v>11.34</v>
@@ -18296,7 +18296,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S34">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T34">
         <v>79.7</v>
@@ -18323,7 +18323,7 @@
         <v>0.9</v>
       </c>
       <c r="AB34">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="AC34">
         <v>0.96</v>
@@ -18376,7 +18376,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="J35">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="K35">
         <v>17.64</v>
@@ -18403,7 +18403,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S35">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T35">
         <v>58.5</v>
@@ -18430,7 +18430,7 @@
         <v>0.89</v>
       </c>
       <c r="AB35">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="AC35">
         <v>0.89</v>
@@ -18471,7 +18471,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="F36">
-        <v>58</v>
+        <v>57.9</v>
       </c>
       <c r="G36">
         <v>17.49</v>
@@ -18510,10 +18510,10 @@
         <v>B5-D09 căng (MN cao)</v>
       </c>
       <c r="S36">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="T36">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U36">
         <v>2.5</v>
@@ -18578,7 +18578,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="F37">
-        <v>106.2</v>
+        <v>105.9</v>
       </c>
       <c r="G37">
         <v>23.39</v>
@@ -18590,7 +18590,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="J37">
-        <v>150.4</v>
+        <v>152.1</v>
       </c>
       <c r="K37">
         <v>23.4</v>
@@ -18617,10 +18617,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S37">
-        <v>33.3</v>
+        <v>34.8</v>
       </c>
       <c r="T37">
-        <v>168.5</v>
+        <v>169.4</v>
       </c>
       <c r="U37">
         <v>5.25</v>
@@ -18641,13 +18641,13 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA37">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AB37">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="AC37">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AD37">
         <v>0</v>
@@ -18659,7 +18659,7 @@
         <v>0.8</v>
       </c>
       <c r="AG37">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AH37" t="str">
         <v>ĐẠT</v>
@@ -18685,7 +18685,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="F38">
-        <v>109.9</v>
+        <v>110.8</v>
       </c>
       <c r="G38">
         <v>17.51</v>
@@ -18724,10 +18724,10 @@
         <v>B6-D13 căng (MN cao)</v>
       </c>
       <c r="S38">
-        <v>70.9</v>
+        <v>71.5</v>
       </c>
       <c r="T38">
-        <v>84</v>
+        <v>84.7</v>
       </c>
       <c r="U38">
         <v>4</v>
@@ -18748,16 +18748,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA38">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AB38">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="AC38">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AD38">
-        <v>0.56</v>
+        <v>0.59</v>
       </c>
       <c r="AE38">
         <v>0.15</v>
@@ -18766,7 +18766,7 @@
         <v>0.62</v>
       </c>
       <c r="AG38">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AH38" t="str">
         <v>ĐẠT</v>
@@ -18792,7 +18792,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="F39">
-        <v>113.9</v>
+        <v>114.9</v>
       </c>
       <c r="G39">
         <v>17.51</v>
@@ -18831,49 +18831,49 @@
         <v>B6-D25 căng (MN cao)</v>
       </c>
       <c r="S39">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="T39">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
       <c r="U39">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="V39">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W39">
-        <v>105.5</v>
+        <v>108.4</v>
       </c>
       <c r="X39">
-        <v>7.01</v>
+        <v>7.21</v>
       </c>
       <c r="Y39">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="Z39" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="AA39">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="AB39">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="AC39">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="AD39">
-        <v>0.55</v>
+        <v>0.28</v>
       </c>
       <c r="AE39">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="AF39">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AG39">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="AH39" t="str">
         <v>ĐẠT</v>
@@ -18899,7 +18899,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="F40">
-        <v>64.6</v>
+        <v>64.9</v>
       </c>
       <c r="G40">
         <v>17.49</v>
@@ -18938,10 +18938,10 @@
         <v>B6-D44 căng (MN cao)</v>
       </c>
       <c r="S40">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="T40">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U40">
         <v>2.75</v>
@@ -18962,16 +18962,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA40">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="AB40">
         <v>0.64</v>
       </c>
       <c r="AC40">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AD40">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AE40">
         <v>0.15</v>
@@ -18980,7 +18980,7 @@
         <v>0.62</v>
       </c>
       <c r="AG40">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AH40" t="str">
         <v>ĐẠT</v>
@@ -19006,7 +19006,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="F41">
-        <v>109</v>
+        <v>109.7</v>
       </c>
       <c r="G41">
         <v>17.51</v>
@@ -19045,10 +19045,10 @@
         <v>B6-D46 căng (MN cao)</v>
       </c>
       <c r="S41">
-        <v>69.8</v>
+        <v>70.2</v>
       </c>
       <c r="T41">
-        <v>83.8</v>
+        <v>84.3</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -19075,10 +19075,10 @@
         <v>0.67</v>
       </c>
       <c r="AC41">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AD41">
-        <v>0.54</v>
+        <v>0.56</v>
       </c>
       <c r="AE41">
         <v>0.15</v>
@@ -19087,7 +19087,7 @@
         <v>0.62</v>
       </c>
       <c r="AG41">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AH41" t="str">
         <v>ĐẠT</v>
@@ -19155,7 +19155,7 @@
         <v>Bê tông đế</v>
       </c>
       <c r="B48">
-        <v>173.3</v>
+        <v>173.6</v>
       </c>
       <c r="C48" t="str">
         <v>m³</v>
@@ -19199,7 +19199,7 @@
         <v>Số đế cạnh B = 3,00 m</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C52" t="str">
         <v>đế</v>
@@ -19210,7 +19210,7 @@
         <v>Số đế cạnh B = 3,25 m</v>
       </c>
       <c r="B53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" t="str">
         <v>đế</v>
@@ -19232,7 +19232,7 @@
         <v>Số đế cạnh B = 3,75 m</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="str">
         <v>đế</v>
@@ -19251,7 +19251,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Số đế cạnh B = 4,75 m</v>
+        <v>Số đế cạnh B = 4,25 m</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -19262,7 +19262,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Số đế cạnh B = 5,25 m</v>
+        <v>Số đế cạnh B = 4,75 m</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -19273,10 +19273,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Số đế mà địa hình IFC cao hơn đáy thiết kế trên 0,5 m (cần kiểm tra khảo sát / nạo vét)</v>
+        <v>Số đế cạnh B = 5,25 m</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" t="str">
         <v>đế</v>
@@ -19284,18 +19284,29 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Số đế có nền cao hơn MNC (lộ khô khi nước chết)</v>
+        <v>Số đế mà địa hình IFC cao hơn đáy thiết kế trên 0,5 m (cần kiểm tra khảo sát / nạo vét)</v>
       </c>
       <c r="B60">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C60" t="str">
         <v>đế</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Số đế có nền cao hơn MNC (lộ khô khi nước chết)</v>
+      </c>
+      <c r="B61">
+        <v>7</v>
+      </c>
+      <c r="C61" t="str">
+        <v>đế</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AI60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AI61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -19497,7 +19508,7 @@
         <v>0.74</v>
       </c>
       <c r="S7">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T7">
         <v>1</v>
@@ -19580,7 +19591,7 @@
         <v>0.74</v>
       </c>
       <c r="S8">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -19663,7 +19674,7 @@
         <v>0.74</v>
       </c>
       <c r="S9">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T9">
         <v>1</v>
@@ -19746,7 +19757,7 @@
         <v>0.74</v>
       </c>
       <c r="S10">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T10">
         <v>1</v>
@@ -19829,7 +19840,7 @@
         <v>0.74</v>
       </c>
       <c r="S11">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T11">
         <v>1</v>
@@ -19912,7 +19923,7 @@
         <v>0.74</v>
       </c>
       <c r="S12">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T12">
         <v>1</v>
@@ -19995,7 +20006,7 @@
         <v>0.74</v>
       </c>
       <c r="S13">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T13">
         <v>1</v>
@@ -20078,7 +20089,7 @@
         <v>0.74</v>
       </c>
       <c r="S14">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T14">
         <v>1</v>
@@ -20161,7 +20172,7 @@
         <v>0.74</v>
       </c>
       <c r="S15">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T15">
         <v>1</v>
@@ -20244,7 +20255,7 @@
         <v>0.74</v>
       </c>
       <c r="S16">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T16">
         <v>1</v>
@@ -20327,7 +20338,7 @@
         <v>0.74</v>
       </c>
       <c r="S17">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T17">
         <v>1</v>
@@ -20410,7 +20421,7 @@
         <v>0.74</v>
       </c>
       <c r="S18">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T18">
         <v>1</v>
@@ -20493,7 +20504,7 @@
         <v>0.74</v>
       </c>
       <c r="S19">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T19">
         <v>1</v>
@@ -20576,7 +20587,7 @@
         <v>0.74</v>
       </c>
       <c r="S20">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T20">
         <v>1</v>
@@ -20659,7 +20670,7 @@
         <v>0.74</v>
       </c>
       <c r="S21">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T21">
         <v>1</v>
@@ -20742,7 +20753,7 @@
         <v>0.74</v>
       </c>
       <c r="S22">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T22">
         <v>1</v>
@@ -20825,7 +20836,7 @@
         <v>0.74</v>
       </c>
       <c r="S23">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T23">
         <v>1</v>
@@ -20908,7 +20919,7 @@
         <v>0.74</v>
       </c>
       <c r="S24">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T24">
         <v>1</v>
@@ -20991,7 +21002,7 @@
         <v>0.74</v>
       </c>
       <c r="S25">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T25">
         <v>1</v>
@@ -21074,7 +21085,7 @@
         <v>0.74</v>
       </c>
       <c r="S26">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T26">
         <v>1</v>
@@ -21157,7 +21168,7 @@
         <v>0.74</v>
       </c>
       <c r="S27">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T27">
         <v>1</v>
@@ -21240,7 +21251,7 @@
         <v>0.74</v>
       </c>
       <c r="S28">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T28">
         <v>1</v>
@@ -21323,7 +21334,7 @@
         <v>0.74</v>
       </c>
       <c r="S29">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T29">
         <v>1</v>
@@ -21406,7 +21417,7 @@
         <v>0.74</v>
       </c>
       <c r="S30">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T30">
         <v>1</v>
@@ -21489,7 +21500,7 @@
         <v>0.74</v>
       </c>
       <c r="S31">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T31">
         <v>1</v>
@@ -21572,7 +21583,7 @@
         <v>0.74</v>
       </c>
       <c r="S32">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T32">
         <v>1</v>
@@ -21655,7 +21666,7 @@
         <v>0.74</v>
       </c>
       <c r="S33">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T33">
         <v>1</v>
@@ -21738,7 +21749,7 @@
         <v>0.74</v>
       </c>
       <c r="S34">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T34">
         <v>1</v>
@@ -21821,7 +21832,7 @@
         <v>0.74</v>
       </c>
       <c r="S35">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T35">
         <v>1</v>
@@ -21904,7 +21915,7 @@
         <v>0.74</v>
       </c>
       <c r="S36">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T36">
         <v>1</v>
@@ -21987,7 +21998,7 @@
         <v>0.74</v>
       </c>
       <c r="S37">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T37">
         <v>1</v>
@@ -22070,7 +22081,7 @@
         <v>0.74</v>
       </c>
       <c r="S38">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T38">
         <v>1</v>
@@ -22153,7 +22164,7 @@
         <v>0.74</v>
       </c>
       <c r="S39">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T39">
         <v>1</v>
@@ -22236,7 +22247,7 @@
         <v>0.74</v>
       </c>
       <c r="S40">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T40">
         <v>1</v>
@@ -22310,10 +22321,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P41">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q41">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R41">
         <v>0.7</v>
@@ -22393,10 +22404,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P42">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q42">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R42">
         <v>0.7</v>
@@ -22476,10 +22487,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P43">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q43">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R43">
         <v>0.7</v>
@@ -22559,10 +22570,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P44">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q44">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R44">
         <v>0.7</v>
@@ -22642,10 +22653,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P45">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q45">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R45">
         <v>0.7</v>
@@ -22725,10 +22736,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P46">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q46">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R46">
         <v>0.7</v>
@@ -22808,10 +22819,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P47">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q47">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R47">
         <v>0.7</v>
@@ -22891,10 +22902,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P48">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q48">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R48">
         <v>0.7</v>
@@ -22974,10 +22985,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P49">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q49">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R49">
         <v>0.7</v>
@@ -23057,10 +23068,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P50">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q50">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R50">
         <v>0.7</v>
@@ -23140,10 +23151,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P51">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q51">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R51">
         <v>0.7</v>
@@ -23223,10 +23234,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P52">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q52">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R52">
         <v>0.7</v>
@@ -23306,10 +23317,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P53">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q53">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R53">
         <v>0.7</v>
@@ -23389,10 +23400,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P54">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q54">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R54">
         <v>0.7</v>
@@ -23472,10 +23483,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P55">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q55">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R55">
         <v>0.7</v>
@@ -23555,10 +23566,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P56">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q56">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R56">
         <v>0.7</v>
@@ -23638,10 +23649,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P57">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q57">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R57">
         <v>0.7</v>
@@ -23721,10 +23732,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P58">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q58">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R58">
         <v>0.7</v>
@@ -23804,10 +23815,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P59">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q59">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R59">
         <v>0.7</v>
@@ -23887,10 +23898,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P60">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q60">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R60">
         <v>0.7</v>
@@ -23970,10 +23981,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P61">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q61">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R61">
         <v>0.7</v>
@@ -24053,10 +24064,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P62">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q62">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R62">
         <v>0.7</v>
@@ -24136,10 +24147,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P63">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q63">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R63">
         <v>0.7</v>
@@ -24219,10 +24230,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P64">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q64">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R64">
         <v>0.7</v>
@@ -24302,10 +24313,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P65">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q65">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R65">
         <v>0.7</v>
@@ -24385,10 +24396,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P66">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q66">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R66">
         <v>0.7</v>
@@ -24468,10 +24479,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P67">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q67">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R67">
         <v>0.7</v>
@@ -24551,10 +24562,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P68">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q68">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R68">
         <v>0.7</v>
@@ -24634,10 +24645,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P69">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q69">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R69">
         <v>0.7</v>
@@ -24717,10 +24728,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P70">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q70">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R70">
         <v>0.7</v>
@@ -24800,10 +24811,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P71">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q71">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R71">
         <v>0.7</v>
@@ -24883,10 +24894,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P72">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q72">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R72">
         <v>0.7</v>
@@ -24966,10 +24977,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P73">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q73">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R73">
         <v>0.7</v>
@@ -25049,10 +25060,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P74">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q74">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R74">
         <v>0.7</v>
@@ -25132,10 +25143,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P75">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q75">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R75">
         <v>0.7</v>
@@ -25215,10 +25226,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P76">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q76">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R76">
         <v>0.7</v>
@@ -25298,10 +25309,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P77">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q77">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R77">
         <v>0.7</v>
@@ -25381,10 +25392,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P78">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q78">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R78">
         <v>0.7</v>
@@ -25464,10 +25475,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P79">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q79">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R79">
         <v>0.7</v>
@@ -25547,10 +25558,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P80">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q80">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R80">
         <v>0.7</v>
@@ -25630,10 +25641,10 @@
         <v>CB500-V</v>
       </c>
       <c r="P81">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q81">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="R81">
         <v>0.7</v>
@@ -25713,16 +25724,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P82">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q82">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R82">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S82">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T82">
         <v>1</v>
@@ -25796,16 +25807,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P83">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q83">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R83">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S83">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T83">
         <v>1</v>
@@ -25879,16 +25890,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P84">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q84">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R84">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S84">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T84">
         <v>1</v>
@@ -25962,16 +25973,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P85">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q85">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R85">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S85">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T85">
         <v>1</v>
@@ -26045,16 +26056,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P86">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q86">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R86">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S86">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T86">
         <v>1</v>
@@ -26128,16 +26139,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P87">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q87">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R87">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S87">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T87">
         <v>1</v>
@@ -26211,16 +26222,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P88">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q88">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R88">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S88">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T88">
         <v>1</v>
@@ -26294,16 +26305,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P89">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q89">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R89">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S89">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T89">
         <v>1</v>
@@ -26377,16 +26388,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P90">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q90">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R90">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S90">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T90">
         <v>1</v>
@@ -26460,16 +26471,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P91">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q91">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R91">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S91">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T91">
         <v>1</v>
@@ -26543,16 +26554,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P92">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q92">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R92">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S92">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T92">
         <v>1</v>
@@ -26626,16 +26637,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P93">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q93">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R93">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S93">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T93">
         <v>1</v>
@@ -26709,16 +26720,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P94">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q94">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R94">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S94">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T94">
         <v>1</v>
@@ -26792,16 +26803,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P95">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q95">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R95">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S95">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T95">
         <v>1</v>
@@ -26875,16 +26886,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P96">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="Q96">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="R96">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S96">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="T96">
         <v>1</v>
@@ -26958,16 +26969,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P97">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q97">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R97">
         <v>0.71</v>
       </c>
       <c r="S97">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T97">
         <v>1</v>
@@ -27041,16 +27052,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P98">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q98">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R98">
         <v>0.71</v>
       </c>
       <c r="S98">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T98">
         <v>1</v>
@@ -27124,16 +27135,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P99">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q99">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R99">
         <v>0.71</v>
       </c>
       <c r="S99">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T99">
         <v>1</v>
@@ -27207,16 +27218,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P100">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q100">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R100">
         <v>0.71</v>
       </c>
       <c r="S100">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T100">
         <v>1</v>
@@ -27290,16 +27301,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P101">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q101">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R101">
         <v>0.71</v>
       </c>
       <c r="S101">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T101">
         <v>1</v>
@@ -27373,16 +27384,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P102">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q102">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R102">
         <v>0.71</v>
       </c>
       <c r="S102">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T102">
         <v>1</v>
@@ -27456,16 +27467,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P103">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q103">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R103">
         <v>0.71</v>
       </c>
       <c r="S103">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T103">
         <v>1</v>
@@ -27539,16 +27550,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P104">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q104">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R104">
         <v>0.71</v>
       </c>
       <c r="S104">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T104">
         <v>1</v>
@@ -27622,16 +27633,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P105">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q105">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R105">
         <v>0.71</v>
       </c>
       <c r="S105">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T105">
         <v>1</v>
@@ -27705,16 +27716,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P106">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q106">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R106">
         <v>0.71</v>
       </c>
       <c r="S106">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T106">
         <v>1</v>
@@ -27788,16 +27799,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P107">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q107">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R107">
         <v>0.71</v>
       </c>
       <c r="S107">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T107">
         <v>1</v>
@@ -27871,16 +27882,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P108">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q108">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R108">
         <v>0.71</v>
       </c>
       <c r="S108">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T108">
         <v>1</v>
@@ -27954,16 +27965,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P109">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q109">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R109">
         <v>0.71</v>
       </c>
       <c r="S109">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T109">
         <v>1</v>
@@ -28037,16 +28048,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P110">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q110">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R110">
         <v>0.71</v>
       </c>
       <c r="S110">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T110">
         <v>1</v>
@@ -28120,16 +28131,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P111">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q111">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R111">
         <v>0.71</v>
       </c>
       <c r="S111">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T111">
         <v>1</v>
@@ -28203,16 +28214,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P112">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q112">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R112">
         <v>0.71</v>
       </c>
       <c r="S112">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T112">
         <v>1</v>
@@ -28286,16 +28297,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P113">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q113">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R113">
         <v>0.71</v>
       </c>
       <c r="S113">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T113">
         <v>1</v>
@@ -28369,16 +28380,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P114">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q114">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R114">
         <v>0.71</v>
       </c>
       <c r="S114">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T114">
         <v>1</v>
@@ -28452,16 +28463,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P115">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q115">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R115">
         <v>0.71</v>
       </c>
       <c r="S115">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T115">
         <v>1</v>
@@ -28535,16 +28546,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P116">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q116">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R116">
         <v>0.71</v>
       </c>
       <c r="S116">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T116">
         <v>1</v>
@@ -28618,16 +28629,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P117">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q117">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R117">
         <v>0.71</v>
       </c>
       <c r="S117">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T117">
         <v>1</v>
@@ -28701,16 +28712,16 @@
         <v>CB500-V</v>
       </c>
       <c r="P118">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q118">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="R118">
         <v>0.71</v>
       </c>
       <c r="S118">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T118">
         <v>1</v>
@@ -28784,16 +28795,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P119">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q119">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R119">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S119">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T119">
         <v>1</v>
@@ -28867,16 +28878,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P120">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q120">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R120">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S120">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T120">
         <v>1</v>
@@ -28950,16 +28961,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P121">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q121">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R121">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S121">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T121">
         <v>1</v>
@@ -29033,16 +29044,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P122">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q122">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R122">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S122">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T122">
         <v>1</v>
@@ -29116,16 +29127,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P123">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q123">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R123">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S123">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T123">
         <v>1</v>
@@ -29199,16 +29210,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P124">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q124">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R124">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S124">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T124">
         <v>1</v>
@@ -29282,16 +29293,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P125">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q125">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R125">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S125">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T125">
         <v>1</v>
@@ -29365,16 +29376,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P126">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q126">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R126">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S126">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T126">
         <v>1</v>
@@ -29448,16 +29459,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P127">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q127">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R127">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S127">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T127">
         <v>1</v>
@@ -29531,16 +29542,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P128">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q128">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R128">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S128">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T128">
         <v>1</v>
@@ -29614,16 +29625,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P129">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q129">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R129">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S129">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T129">
         <v>1</v>
@@ -29697,16 +29708,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P130">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q130">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R130">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S130">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T130">
         <v>1</v>
@@ -29780,16 +29791,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P131">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q131">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R131">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S131">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T131">
         <v>1</v>
@@ -29863,16 +29874,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P132">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q132">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R132">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S132">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T132">
         <v>1</v>
@@ -29946,16 +29957,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P133">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q133">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R133">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S133">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T133">
         <v>1</v>
@@ -30029,16 +30040,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P134">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q134">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R134">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S134">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T134">
         <v>1</v>
@@ -30112,16 +30123,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P135">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q135">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R135">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S135">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T135">
         <v>1</v>
@@ -30195,16 +30206,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P136">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q136">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R136">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S136">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T136">
         <v>1</v>
@@ -30278,16 +30289,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P137">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q137">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R137">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S137">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T137">
         <v>1</v>
@@ -30361,16 +30372,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P138">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q138">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R138">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S138">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T138">
         <v>1</v>
@@ -30444,16 +30455,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P139">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q139">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R139">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S139">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T139">
         <v>1</v>
@@ -30527,16 +30538,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P140">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q140">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R140">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S140">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T140">
         <v>1</v>
@@ -30610,16 +30621,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P141">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q141">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R141">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S141">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T141">
         <v>1</v>
@@ -30693,16 +30704,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P142">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q142">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R142">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S142">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T142">
         <v>1</v>
@@ -30776,16 +30787,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P143">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q143">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R143">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S143">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T143">
         <v>1</v>
@@ -30859,16 +30870,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P144">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q144">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R144">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S144">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T144">
         <v>1</v>
@@ -30942,16 +30953,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P145">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q145">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="R145">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S145">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="T145">
         <v>1</v>
@@ -31025,16 +31036,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P146">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q146">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R146">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S146">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T146">
         <v>1</v>
@@ -31108,16 +31119,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P147">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q147">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R147">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S147">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T147">
         <v>1</v>
@@ -31191,16 +31202,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P148">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q148">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R148">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S148">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T148">
         <v>1</v>
@@ -31274,16 +31285,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P149">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q149">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R149">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S149">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T149">
         <v>1</v>
@@ -31357,16 +31368,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P150">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q150">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R150">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S150">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T150">
         <v>1</v>
@@ -31440,16 +31451,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P151">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q151">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R151">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S151">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T151">
         <v>1</v>
@@ -31523,16 +31534,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P152">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q152">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R152">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S152">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T152">
         <v>1</v>
@@ -31606,16 +31617,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P153">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q153">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R153">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S153">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T153">
         <v>1</v>
@@ -31689,16 +31700,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P154">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q154">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R154">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S154">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T154">
         <v>1</v>
@@ -31772,16 +31783,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P155">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q155">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R155">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S155">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T155">
         <v>1</v>
@@ -31855,16 +31866,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P156">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q156">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R156">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S156">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T156">
         <v>1</v>
@@ -31938,16 +31949,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P157">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q157">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R157">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S157">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T157">
         <v>1</v>
@@ -32021,16 +32032,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P158">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q158">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R158">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S158">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T158">
         <v>1</v>
@@ -32104,16 +32115,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P159">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q159">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R159">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S159">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T159">
         <v>1</v>
@@ -32187,16 +32198,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P160">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q160">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R160">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S160">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T160">
         <v>1</v>
@@ -32270,16 +32281,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P161">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q161">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R161">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S161">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T161">
         <v>1</v>
@@ -32353,16 +32364,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P162">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q162">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R162">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S162">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T162">
         <v>1</v>
@@ -32436,16 +32447,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P163">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q163">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R163">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S163">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T163">
         <v>1</v>
@@ -32519,16 +32530,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P164">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q164">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R164">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S164">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T164">
         <v>1</v>
@@ -32602,16 +32613,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P165">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q165">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R165">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S165">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T165">
         <v>1</v>
@@ -32685,16 +32696,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P166">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q166">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R166">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S166">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T166">
         <v>1</v>
@@ -32768,16 +32779,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P167">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q167">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R167">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S167">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T167">
         <v>1</v>
@@ -32851,16 +32862,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P168">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q168">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R168">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S168">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T168">
         <v>1</v>
@@ -32934,16 +32945,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P169">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q169">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R169">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S169">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T169">
         <v>1</v>
@@ -33017,16 +33028,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P170">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q170">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R170">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S170">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T170">
         <v>1</v>
@@ -33100,16 +33111,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P171">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q171">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R171">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S171">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T171">
         <v>1</v>
@@ -33183,16 +33194,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P172">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q172">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R172">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S172">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T172">
         <v>1</v>
@@ -33266,16 +33277,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P173">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q173">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R173">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S173">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T173">
         <v>1</v>
@@ -33349,16 +33360,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P174">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q174">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R174">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S174">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T174">
         <v>1</v>
@@ -33432,16 +33443,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P175">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q175">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R175">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S175">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T175">
         <v>1</v>
@@ -33515,16 +33526,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P176">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q176">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R176">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S176">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T176">
         <v>1</v>
@@ -33598,16 +33609,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P177">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q177">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R177">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S177">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T177">
         <v>1</v>
@@ -33681,16 +33692,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P178">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q178">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R178">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S178">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T178">
         <v>1</v>
@@ -33764,16 +33775,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P179">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q179">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R179">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S179">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T179">
         <v>1</v>
@@ -33847,16 +33858,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P180">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q180">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R180">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S180">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T180">
         <v>1</v>
@@ -33930,16 +33941,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P181">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q181">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R181">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S181">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T181">
         <v>1</v>
@@ -34013,16 +34024,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P182">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q182">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R182">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S182">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T182">
         <v>1</v>
@@ -34096,16 +34107,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P183">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q183">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R183">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S183">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T183">
         <v>1</v>
@@ -34179,16 +34190,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P184">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q184">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R184">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S184">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T184">
         <v>1</v>
@@ -34262,16 +34273,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P185">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q185">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R185">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S185">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T185">
         <v>1</v>
@@ -34345,16 +34356,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P186">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q186">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R186">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S186">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T186">
         <v>1</v>
@@ -34428,16 +34439,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P187">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q187">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R187">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S187">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T187">
         <v>1</v>
@@ -34511,16 +34522,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P188">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q188">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R188">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S188">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T188">
         <v>1</v>
@@ -34594,16 +34605,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P189">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q189">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R189">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S189">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T189">
         <v>1</v>
@@ -34677,16 +34688,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P190">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="Q190">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="R190">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S190">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T190">
         <v>1</v>
